--- a/LISTAS/ma/CAÑOS EXTENSIBLES - CURVOS.xlsx
+++ b/LISTAS/ma/CAÑOS EXTENSIBLES - CURVOS.xlsx
@@ -752,7 +752,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="31" t="n">
-        <v>45163.60855777778</v>
+        <v>45214</v>
       </c>
     </row>
     <row r="2">
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="D10" s="19" t="n">
-        <v>744.36</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="11">
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="D11" s="19" t="n">
-        <v>964.92</v>
+        <v>1758.12</v>
       </c>
     </row>
     <row r="12">
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="D12" s="19" t="n">
-        <v>827.01</v>
+        <v>1441.2</v>
       </c>
     </row>
     <row r="13">
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="D13" s="19" t="n">
-        <v>1075.42</v>
+        <v>1959.6</v>
       </c>
     </row>
     <row r="14">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="D14" s="19" t="n">
-        <v>1265.55</v>
+        <v>2304.12</v>
       </c>
     </row>
     <row r="15">
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="D15" s="19" t="n">
-        <v>1053.06</v>
+        <v>1911.6</v>
       </c>
     </row>
     <row r="16">
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="D16" s="21" t="n">
-        <v>1641.63</v>
+        <v>2986.8</v>
       </c>
     </row>
     <row r="17">
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="D17" s="22" t="n">
-        <v>174.55</v>
+        <v>238.8</v>
       </c>
     </row>
     <row r="18">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="C18" s="16" t="n"/>
       <c r="D18" s="22" t="n">
-        <v>1197.32</v>
+        <v>2509.2</v>
       </c>
     </row>
     <row r="19">
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="D19" s="22" t="n">
-        <v>2005.15</v>
+        <v>4218</v>
       </c>
     </row>
     <row r="20">
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="D20" s="22" t="n">
-        <v>2005.15</v>
+        <v>4218</v>
       </c>
     </row>
     <row r="22" ht="196.5" customHeight="1" s="30"/>
@@ -1105,7 +1105,7 @@
         </is>
       </c>
       <c r="D25" s="25" t="n">
-        <v>859.76</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="26">
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="D26" s="25" t="n">
-        <v>1472.99</v>
+        <v>2586</v>
       </c>
     </row>
     <row r="27">
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="D27" s="25" t="n">
-        <v>1128.94</v>
+        <v>1982.4</v>
       </c>
     </row>
     <row r="28">
@@ -1165,7 +1165,7 @@
         </is>
       </c>
       <c r="D28" s="25" t="n">
-        <v>1550.75</v>
+        <v>2721.6</v>
       </c>
     </row>
     <row r="29">
@@ -1185,7 +1185,7 @@
         </is>
       </c>
       <c r="D29" s="25" t="n">
-        <v>1217.52</v>
+        <v>2168.4</v>
       </c>
     </row>
     <row r="30">
@@ -1205,7 +1205,7 @@
         </is>
       </c>
       <c r="D30" s="25" t="n">
-        <v>1923.22</v>
+        <v>3439.2</v>
       </c>
     </row>
     <row r="31">
@@ -1225,7 +1225,7 @@
         </is>
       </c>
       <c r="D31" s="25" t="n">
-        <v>1579.31</v>
+        <v>2826</v>
       </c>
     </row>
     <row r="32">
@@ -1245,7 +1245,7 @@
         </is>
       </c>
       <c r="D32" s="25" t="n">
-        <v>2002.27</v>
+        <v>3566.4</v>
       </c>
     </row>
     <row r="33">

--- a/LISTAS/ma/CAÑOS EXTENSIBLES - CURVOS.xlsx
+++ b/LISTAS/ma/CAÑOS EXTENSIBLES - CURVOS.xlsx
@@ -752,7 +752,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="31" t="n">
-        <v>45214</v>
+        <v>45216</v>
       </c>
     </row>
     <row r="2">
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="D10" s="19" t="n">
-        <v>1400</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="11">
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="D11" s="19" t="n">
-        <v>1758.12</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="12">

--- a/LISTAS/ma/CAÑOS EXTENSIBLES - CURVOS.xlsx
+++ b/LISTAS/ma/CAÑOS EXTENSIBLES - CURVOS.xlsx
@@ -752,7 +752,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="31" t="n">
-        <v>45216</v>
+        <v>45219</v>
       </c>
     </row>
     <row r="2">
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="D10" s="19" t="n">
-        <v>1000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="11">
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="D11" s="19" t="n">
-        <v>1600</v>
+        <v>1758.12</v>
       </c>
     </row>
     <row r="12">
@@ -1265,8 +1265,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A47:D47"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A47:D47"/>
   </mergeCells>
   <pageMargins left="0.7480314960629921" right="0.7480314960629921" top="0.984251968503937" bottom="0.3937007874015748" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/CAÑOS EXTENSIBLES - CURVOS.xlsx
+++ b/LISTAS/ma/CAÑOS EXTENSIBLES - CURVOS.xlsx
@@ -752,7 +752,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="31" t="n">
-        <v>45219</v>
+        <v>45223</v>
       </c>
     </row>
     <row r="2">

--- a/LISTAS/ma/CAÑOS EXTENSIBLES - CURVOS.xlsx
+++ b/LISTAS/ma/CAÑOS EXTENSIBLES - CURVOS.xlsx
@@ -752,7 +752,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="31" t="n">
-        <v>45223</v>
+        <v>45237</v>
       </c>
     </row>
     <row r="2">
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="D10" s="19" t="n">
-        <v>1500</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="11">

--- a/LISTAS/ma/CAÑOS EXTENSIBLES - CURVOS.xlsx
+++ b/LISTAS/ma/CAÑOS EXTENSIBLES - CURVOS.xlsx
@@ -752,7 +752,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="31" t="n">
-        <v>45237</v>
+        <v>45238</v>
       </c>
     </row>
     <row r="2">
@@ -1265,8 +1265,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
     <mergeCell ref="A47:D47"/>
-    <mergeCell ref="A1:D1"/>
   </mergeCells>
   <pageMargins left="0.7480314960629921" right="0.7480314960629921" top="0.984251968503937" bottom="0.3937007874015748" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/CAÑOS EXTENSIBLES - CURVOS.xlsx
+++ b/LISTAS/ma/CAÑOS EXTENSIBLES - CURVOS.xlsx
@@ -752,7 +752,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="31" t="n">
-        <v>45238</v>
+        <v>45239</v>
       </c>
     </row>
     <row r="2">

--- a/LISTAS/ma/CAÑOS EXTENSIBLES - CURVOS.xlsx
+++ b/LISTAS/ma/CAÑOS EXTENSIBLES - CURVOS.xlsx
@@ -1265,8 +1265,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A47:D47"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A47:D47"/>
   </mergeCells>
   <pageMargins left="0.7480314960629921" right="0.7480314960629921" top="0.984251968503937" bottom="0.3937007874015748" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/CAÑOS EXTENSIBLES - CURVOS.xlsx
+++ b/LISTAS/ma/CAÑOS EXTENSIBLES - CURVOS.xlsx
@@ -752,7 +752,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="31" t="n">
-        <v>45239</v>
+        <v>45253</v>
       </c>
     </row>
     <row r="2">
@@ -1265,8 +1265,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
     <mergeCell ref="A47:D47"/>
-    <mergeCell ref="A1:D1"/>
   </mergeCells>
   <pageMargins left="0.7480314960629921" right="0.7480314960629921" top="0.984251968503937" bottom="0.3937007874015748" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/CAÑOS EXTENSIBLES - CURVOS.xlsx
+++ b/LISTAS/ma/CAÑOS EXTENSIBLES - CURVOS.xlsx
@@ -752,7 +752,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="31" t="n">
-        <v>45253</v>
+        <v>45256</v>
       </c>
     </row>
     <row r="2">

--- a/LISTAS/ma/CAÑOS EXTENSIBLES - CURVOS.xlsx
+++ b/LISTAS/ma/CAÑOS EXTENSIBLES - CURVOS.xlsx
@@ -752,7 +752,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="31" t="n">
-        <v>45256</v>
+        <v>45266</v>
       </c>
     </row>
     <row r="2">

--- a/LISTAS/ma/CAÑOS EXTENSIBLES - CURVOS.xlsx
+++ b/LISTAS/ma/CAÑOS EXTENSIBLES - CURVOS.xlsx
@@ -752,7 +752,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="31" t="n">
-        <v>45266</v>
+        <v>45261.57770068407</v>
       </c>
     </row>
     <row r="2">
@@ -786,7 +786,7 @@
       <c r="C5" s="3" t="n"/>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E5" s="5" t="n"/>
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="D10" s="19" t="n">
-        <v>1600</v>
+        <v>1593.71</v>
       </c>
     </row>
     <row r="11">
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="D11" s="19" t="n">
-        <v>1758.12</v>
+        <v>2166</v>
       </c>
     </row>
     <row r="12">
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="D12" s="19" t="n">
-        <v>1441.2</v>
+        <v>1775.55</v>
       </c>
     </row>
     <row r="13">
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="D13" s="19" t="n">
-        <v>1959.6</v>
+        <v>2414.22</v>
       </c>
     </row>
     <row r="14">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="D14" s="19" t="n">
-        <v>2304.12</v>
+        <v>2838.67</v>
       </c>
     </row>
     <row r="15">
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="D15" s="19" t="n">
-        <v>1911.6</v>
+        <v>2355.09</v>
       </c>
     </row>
     <row r="16">
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="D16" s="21" t="n">
-        <v>2986.8</v>
+        <v>3679.73</v>
       </c>
     </row>
     <row r="17">
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="D17" s="22" t="n">
-        <v>238.8</v>
+        <v>294.2</v>
       </c>
     </row>
     <row r="18">
@@ -1010,8 +1010,10 @@
         </is>
       </c>
       <c r="C18" s="16" t="n"/>
-      <c r="D18" s="22" t="n">
-        <v>2509.2</v>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -1030,8 +1032,10 @@
           <t>1 x 12</t>
         </is>
       </c>
-      <c r="D19" s="22" t="n">
-        <v>4218</v>
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -1050,10 +1054,13 @@
           <t>1 x 12</t>
         </is>
       </c>
-      <c r="D20" s="22" t="n">
-        <v>4218</v>
-      </c>
-    </row>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
     <row r="22" ht="196.5" customHeight="1" s="30"/>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
@@ -1105,7 +1112,7 @@
         </is>
       </c>
       <c r="D25" s="25" t="n">
-        <v>1512</v>
+        <v>1862.78</v>
       </c>
     </row>
     <row r="26">
@@ -1125,7 +1132,7 @@
         </is>
       </c>
       <c r="D26" s="25" t="n">
-        <v>2586</v>
+        <v>3185.95</v>
       </c>
     </row>
     <row r="27">
@@ -1145,7 +1152,7 @@
         </is>
       </c>
       <c r="D27" s="25" t="n">
-        <v>1982.4</v>
+        <v>2442.31</v>
       </c>
     </row>
     <row r="28">
@@ -1165,7 +1172,7 @@
         </is>
       </c>
       <c r="D28" s="25" t="n">
-        <v>2721.6</v>
+        <v>3353.01</v>
       </c>
     </row>
     <row r="29">
@@ -1185,7 +1192,7 @@
         </is>
       </c>
       <c r="D29" s="25" t="n">
-        <v>2168.4</v>
+        <v>2671.46</v>
       </c>
     </row>
     <row r="30">
@@ -1205,7 +1212,7 @@
         </is>
       </c>
       <c r="D30" s="25" t="n">
-        <v>3439.2</v>
+        <v>4237.09</v>
       </c>
     </row>
     <row r="31">
@@ -1225,7 +1232,7 @@
         </is>
       </c>
       <c r="D31" s="25" t="n">
-        <v>2826</v>
+        <v>3481.63</v>
       </c>
     </row>
     <row r="32">
@@ -1245,12 +1252,25 @@
         </is>
       </c>
       <c r="D32" s="25" t="n">
-        <v>3566.4</v>
+        <v>4393.8</v>
       </c>
     </row>
     <row r="33">
       <c r="D33" s="12" t="n"/>
     </row>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
     <row r="47">
       <c r="A47" s="29" t="n"/>
     </row>
@@ -1265,8 +1285,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A47:D47"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A47:D47"/>
   </mergeCells>
   <pageMargins left="0.7480314960629921" right="0.7480314960629921" top="0.984251968503937" bottom="0.3937007874015748" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/CAÑOS EXTENSIBLES - CURVOS.xlsx
+++ b/LISTAS/ma/CAÑOS EXTENSIBLES - CURVOS.xlsx
@@ -752,7 +752,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="31" t="n">
-        <v>45261.57770068407</v>
+        <v>45286</v>
       </c>
     </row>
     <row r="2">
@@ -786,7 +786,7 @@
       <c r="C5" s="3" t="n"/>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="E5" s="5" t="n"/>
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="D10" s="19" t="n">
-        <v>1593.71</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="11">
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="D11" s="19" t="n">
-        <v>2166</v>
+        <v>1758.12</v>
       </c>
     </row>
     <row r="12">
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="D12" s="19" t="n">
-        <v>1775.55</v>
+        <v>1441.2</v>
       </c>
     </row>
     <row r="13">
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="D13" s="19" t="n">
-        <v>2414.22</v>
+        <v>1959.6</v>
       </c>
     </row>
     <row r="14">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="D14" s="19" t="n">
-        <v>2838.67</v>
+        <v>2304.12</v>
       </c>
     </row>
     <row r="15">
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="D15" s="19" t="n">
-        <v>2355.09</v>
+        <v>1911.6</v>
       </c>
     </row>
     <row r="16">
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="D16" s="21" t="n">
-        <v>3679.73</v>
+        <v>2986.8</v>
       </c>
     </row>
     <row r="17">
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="D17" s="22" t="n">
-        <v>294.2</v>
+        <v>238.8</v>
       </c>
     </row>
     <row r="18">
@@ -1012,7 +1012,7 @@
       <c r="C18" s="16" t="n"/>
       <c r="D18" s="22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>********</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D19" s="22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>********</t>
         </is>
       </c>
     </row>
@@ -1056,11 +1056,10 @@
       </c>
       <c r="D20" s="22" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="21"/>
+          <t>********</t>
+        </is>
+      </c>
+    </row>
     <row r="22" ht="196.5" customHeight="1" s="30"/>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
@@ -1112,7 +1111,7 @@
         </is>
       </c>
       <c r="D25" s="25" t="n">
-        <v>1862.78</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="26">
@@ -1132,7 +1131,7 @@
         </is>
       </c>
       <c r="D26" s="25" t="n">
-        <v>3185.95</v>
+        <v>2586</v>
       </c>
     </row>
     <row r="27">
@@ -1152,7 +1151,7 @@
         </is>
       </c>
       <c r="D27" s="25" t="n">
-        <v>2442.31</v>
+        <v>1982.4</v>
       </c>
     </row>
     <row r="28">
@@ -1172,7 +1171,7 @@
         </is>
       </c>
       <c r="D28" s="25" t="n">
-        <v>3353.01</v>
+        <v>2721.6</v>
       </c>
     </row>
     <row r="29">
@@ -1192,7 +1191,7 @@
         </is>
       </c>
       <c r="D29" s="25" t="n">
-        <v>2671.46</v>
+        <v>2168.4</v>
       </c>
     </row>
     <row r="30">
@@ -1212,7 +1211,7 @@
         </is>
       </c>
       <c r="D30" s="25" t="n">
-        <v>4237.09</v>
+        <v>3439.2</v>
       </c>
     </row>
     <row r="31">
@@ -1232,7 +1231,7 @@
         </is>
       </c>
       <c r="D31" s="25" t="n">
-        <v>3481.63</v>
+        <v>2826</v>
       </c>
     </row>
     <row r="32">
@@ -1252,25 +1251,12 @@
         </is>
       </c>
       <c r="D32" s="25" t="n">
-        <v>4393.8</v>
+        <v>3566.4</v>
       </c>
     </row>
     <row r="33">
       <c r="D33" s="12" t="n"/>
     </row>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
     <row r="47">
       <c r="A47" s="29" t="n"/>
     </row>
